--- a/manual/scenarios/ParaBank_Testing_Documentation.xlsx
+++ b/manual/scenarios/ParaBank_Testing_Documentation.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="251">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -390,6 +390,465 @@
   </si>
   <si>
     <t xml:space="preserve">Error message "Social Security Number is required" appears.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Default Account for New User</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User has just registered a new account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in with the new account.
+2. Go to "Accounts Overview" page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The page should display exactly one default account created automatically by the system with an initial balance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Account Data Columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in and has at least one account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to "Accounts Overview" page.
+2. Check the table headers and data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table must display columns: "Account", "Balance", and "Available Amount". Data format should be in correct currency (e.g., $100.00).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Total Balance Calculation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in and has multiple accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to "Accounts Overview" page.
+2. Manually sum the values in the "Balance" column.
+3. Compare with the "Total" displayed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E.g., Acc1: $100, Acc2: $50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The "Total" row at the bottom must exactly match the mathematical sum of all individual account balances ($150).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Account Navigation Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to "Accounts Overview".
+2. Click on any Account Number (Hyperlink).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid Account Number (e.g., 12345)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is redirected to the "Account Details/Activity" page specifically for account 12345.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Balance Update After Transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Check current balance.
+2. Perform a valid fund transfer.
+3. Return to "Accounts Overview".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer: $20 from Acc A to Acc B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The balances for both accounts and the "Total" amount must update immediately to reflect the transfer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify UI Responsiveness &amp; Formatting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is on "Accounts Overview" page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Resize the browser window to mobile size.
+2. Check the table display.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The table should not break or overlap; columns should remain readable and aligned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid Fund Transfer (Happy Path)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in &amp; has 2 accounts with sufficient balance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to "Transfer Funds".
+2. Enter a valid amount.
+3. Select "From" and "To" accounts.
+4. Click "Transfer".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount: 100From: Acc ATo: Acc B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Transfer Complete" message appears. The amount is deducted from Acc A and added to Acc B correctly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer with Insufficient Funds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter an amount GREATER than the current balance in the "From" account.
+2. Click "Transfer".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount: 9999999 (Higher than balance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System blocks the transfer and displays an error like "Insufficient Funds".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer a Negative Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter a negative number in the amount field.
+2. Click "Transfer".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount: -500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System rejects the input with a validation error (e.g., "Amount must be greater than zero").</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer Zero Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 0 in the amount field.
+2. Click "Transfer".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount: 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System prevents the transfer and shows a validation error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer to the SAME Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select the exact same account number for BOTH "From" and "To" dropdowns.
+2. Enter amount &amp; Transfer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From: Acc ATo: Acc A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System should block the operation and warn the user "Cannot transfer to the same account".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invalid Input Types (Text/Symbols)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter letters or special characters instead of numbers.
+2. Click "Transfer".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount: Fifty or $100 or 100,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System blocks submission and shows an error "Please enter a valid number".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer with Empty Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Leave the amount field completely blank.
+2. Click "Transfer".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount: [Blank]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System prevents transfer and shows "Amount is required".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay Bill - Valid Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is logged in, has sufficient balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to Bill Pay
+2. Enter valid Payee Name
+3. Enter valid Address, City, State, Zip Code, Phone
+4. Enter valid Account number in both fields
+5. Enter valid Amount (&lt;= balance)
+6. Select From Account
+7. Click Send Payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee: Water Corp
+Amount: 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Success message 'Bill Payment Complete' appears; balance is deducted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay Bill - Missing Mandatory Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to Bill Pay
+2. Fill all fields EXCEPT 'Payee Name'
+3. Click Send Payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing Payee Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error message 'Payee name is required' appears; payment is not processed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay Bill - Account Mismatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to Bill Pay
+2. Fill valid details
+3. Enter different values in 'Account' and 'Verify Account'
+4. Click Send Payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account: 12345
+Verify: 12346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error message 'The account numbers do not match' appears.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay Bill - Insufficient Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to Bill Pay
+2. Fill valid details
+3. Enter Amount &gt; current balance
+4. Click Send Payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount &gt; Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System should block payment or show appropriate error (Note actual behavior as ParaBank might allow overdraft).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay Bill - Invalid Amount Format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to Bill Pay
+2. Fill valid details
+3. Enter invalid Amount (e.g., 'fifty' or '-50')
+4. Click Send Payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount: -50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error message indicating invalid amount format appears; payment is not processed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay Bill - Verify Transaction History</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_13 is executed successfully</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Go to Accounts Overview
+2. Click on the 'From Account' used in TC_13
+3. Check transaction list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check account used in TC_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 'Funds Transfer Sent' transaction should be recorded matching the payee and amount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Successful Form Submission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User is on the "Contact Us" page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill in Name, Email, Phone, and Message with valid data.
+2. Click "Send to Customer Care".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name: John DoeEmail: test@test.comPhone: 123456789Message: Hello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Success message appears (e.g., "Thank you, Customer Care will contact you.").</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit with Empty Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Leave all fields blank.
+2. Click "Send to Customer Care".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System prevents submission; validation errors appear for all required fields (Name, Email, Phone, Message).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing Name Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill all fields EXCEPT "Name".
+2. Click "Send".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing: Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error message "Name is required" appears; message is not sent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing Message Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill all fields EXCEPT "Message".
+2. Click "Send".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing: Message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error message "Message is required" appears; message is not sent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invalid Email Format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill all fields.
+2. Enter an invalid email format.
+3. Click "Send".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email: johndoe.com (missing @)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System should display an error stating the email format is invalid. (Note: Test actual behavior, dummy apps sometimes skip this validation).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special Characters in Phone Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill all fields.
+2. Enter letters or special characters in the Phone field.
+3. Click "Send".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone: abc-$#@!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System should ideally reject non-numeric characters for phone numbers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exceeding Max Length in Message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill basic fields.
+2. Enter a very large amount of text in the Message field (&gt;5000 chars).
+3. Click "Send".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Message: [Very long string]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System handles it gracefully (truncates the message or shows an error) without crashing.</t>
   </si>
 </sst>
 </file>
@@ -399,7 +858,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,12 +888,6 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -492,21 +945,33 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -518,7 +983,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -776,99 +1241,99 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -891,85 +1356,85 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -989,235 +1454,235 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1048576"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="100.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="37.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="92.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="100.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="37.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="106.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="48.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="48.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="48.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="48.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>67</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="48.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="33.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1238,14 +1703,14 @@
       <c r="G8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="33.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>87</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1266,14 +1731,14 @@
       <c r="G9" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="48.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>92</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1294,14 +1759,14 @@
       <c r="G10" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="48.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="11" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1322,14 +1787,14 @@
       <c r="G11" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="33.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="12" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1350,14 +1815,14 @@
       <c r="G12" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="33.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="13" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1378,43 +1843,752 @@
       <c r="G13" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="61.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="108.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="61.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="61.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="61.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="30.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="46.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
